--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_919_France_Atlantic_Coast.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_919_France_Atlantic_Coast.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra9c89171d9fe477f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R905eb3e58d474894"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R54218694a6154f5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R78a38dc2a15c4ec0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rcf055a43708e4556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R83c27ca2dd7e4914"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R407bb49abfd945e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R6bdeefa5443a436a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb749530e49674bd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R02fdd6cd9cbb45d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R6673a666a78f4665"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R4c52a1c3daf84065"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ919CommercialTable" displayName="EEZ919CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ919CommercialTable" displayName="EEZ919CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ919FunctionalTable" displayName="EEZ919FunctionalTable" ref="A1:O28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O28"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ919FunctionalTable" displayName="EEZ919FunctionalTable" ref="A1:E28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E28"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ919ValidationTable" displayName="EEZ919ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ919ValidationTable" displayName="EEZ919ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -24010,7 +23964,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R817e00c3626d4ecf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56a04d0d00c149d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24020,20 +23974,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -24041,714 +23985,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4110.4636680023</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4110.4636680023</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$349,A2,'Species'!$U$2:$U$349))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>529530.2977554877</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>529530.2977554877</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>41985.4260441122</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.2375122140525825</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1727.8745743883326</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>41985.4260441122</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1967.7258439412985</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$349,A3,'Species'!$U$2:$U$349))</x:f>
-        <x:v>82615807.89588566</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.2375122140525825</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1727.8745743883326</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>72545550.15648319</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>10070257.739402473</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1388128936603361</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.138812893660336</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>10899.7126441877</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.962228030669748</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>91.67016871893152</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>10899.7126441877</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>113.48221616659434</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$349,A4,'Species'!$U$2:$U$349))</x:f>
-        <x:v>1236923.5464414703</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.962228030669748</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>91.67016871893152</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>999178.4970805577</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>237745.04936091253</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2379405181912602</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.23794051819126025</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>17879.9078796918</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.4241258421432694</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>265.53748778918595</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>17879.9078796918</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>394.68550947892794</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$349,A5,'Species'!$U$2:$U$349))</x:f>
-        <x:v>7056940.550932457</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.4241258421432694</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>265.53748778918595</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4747785.820275431</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>2309154.730657026</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.486364553513719</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.48636455351371904</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>42524.6525898804</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.1973433757476415</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>157.5227829075606</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>42524.6525898804</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>168.58643374241333</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$349,A6,'Species'!$U$2:$U$349))</x:f>
-        <x:v>7169079.526263018</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.1973433757476415</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>157.5227829075606</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>6698601.618135165</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>470477.9081278527</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0702352423607526</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.07023524236075257</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>31930.468714293904</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.4225312685123903</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>26.456431699700243</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>31930.468714293904</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>134.99890423757714</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$349,A7,'Species'!$U$2:$U$349))</x:f>
-        <x:v>4310578.288221915</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.4225312685123903</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>26.456431699700243</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>844766.2646791321</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3465812.023542783</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>5.102687534355084</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>4.102687534355084</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>46874.181902961</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.8157763654498607</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>654.2991640760863</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>46874.181902961</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1187.9510233695034</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$349,A8,'Species'!$U$2:$U$349))</x:f>
-        <x:v>55684232.361230776</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.8157763654498607</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>654.2991640760863</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>30669738.035857793</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>25014494.325372983</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.8156083464464896</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.8156083464464896</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>49096.86875954799</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6544412840200753</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>451.27500949395693</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>49096.86875954799</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>604.6674365459224</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$349,A9,'Species'!$U$2:$U$349))</x:f>
-        <x:v>29687277.775267467</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6544412840200753</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>451.27500949395693</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>22156189.915588576</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>7531087.859678891</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.339908977507915</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.339908977507915</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>46.80293075110001</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7023372606380938</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>503.89176477975263</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>46.80293075110001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>870.2348220139845</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$349,A10,'Species'!$U$2:$U$349))</x:f>
-        <x:v>40729.54011191636</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7023372606380938</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>503.89176477975263</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>23583.611373036336</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>17145.928738880022</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.7270272761737984</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.7270272761737985</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>5779.9838405798</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.80257743306321</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>634.7130578303929</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>5779.9838405798</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>652.5831355573507</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$349,A11,'Species'!$U$2:$U$349))</x:f>
-        <x:v>3771919.9781563845</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.80257743306321</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>634.7130578303929</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3668631.217664663</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>103288.76049172133</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0281545771061371</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.028154577106137082</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>14457.683912940001</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.002330414475547</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1005.3804002755195</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>14457.683912940001</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1129.3177067085978</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$349,A12,'Species'!$U$2:$U$349))</x:f>
-        <x:v>16327318.44087919</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.002330414475547</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1005.3804002755195</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>14535472.039448557</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1791846.401430633</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.123274042739558</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.12327404273955808</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>5240.099094285898</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.344616275220509</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2211.140173553197</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>5240.099094285898</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2246.957675477427</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$349,A13,'Species'!$U$2:$U$349))</x:f>
-        <x:v>11774280.880168013</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.344616275220509</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2211.140173553197</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>11586593.620775271</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>187687.25939274207</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0161986573047845</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.016198657304784606</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fc99c2f9e8f4827"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60ab71a665654685"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24758,20 +24238,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -24779,1524 +24249,535 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>11228.591797147701</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.041339104523692</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1099.8642970038964</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>11228.591797147701</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1265.2624108840848</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$349,A2,'Species'!$U$2:$U$349))</x:f>
-        <x:v>14207115.12809236</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.041339104523692</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1099.8642970038964</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>12349927.223313574</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>1857187.904778786</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1503804736009198</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.15038047360091966</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1417.4584356951</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.334539531020119</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2160.4266755039484</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1417.4584356951</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2201.26990356699</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$349,A3,'Species'!$U$2:$U$349))</x:f>
-        <x:v>3120208.5940527692</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.334539531020119</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2160.4266755039484</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3062315.0158937923</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>57893.578158976976</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0189051674496263</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.018905167449626236</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>210.7993035768</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.5435780613919015</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>349.60534306373796</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>210.7993035768</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>354.9697941954303</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$349,A4,'Species'!$U$2:$U$349))</x:f>
-        <x:v>74827.38540719674</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.5435780613919015</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>349.60534306373796</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>73696.5628445642</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1130.8225626325293</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0153443053377886</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.015344305337788732</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3705.1558851283007</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.16553736530653</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1463.9874889278976</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3705.1558851283007</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1721.3403519089004</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$349,A5,'Species'!$U$2:$U$349))</x:f>
-        <x:v>6377834.335184082</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.16553736530653</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1463.9874889278976</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>5424301.860355403</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>953532.4748286791</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.1757889769737488</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.17578897697374887</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>28496.770487258098</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.329317355508751</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2134.6041798944416</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>28496.770487258098</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2294.7107564259345</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$349,A6,'Species'!$U$2:$U$349))</x:f>
-        <x:v>65391845.76051228</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.329317355508751</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2134.6041798944416</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>60829325.395593695</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>4562520.364918582</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0750052764065188</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.07500527640651886</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3454.7824466609</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4010213258932405</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>251.78005605239298</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3454.7824466609</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>452.32718676599046</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$349,A7,'Species'!$U$2:$U$349))</x:f>
-        <x:v>1562692.0249866503</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4010213258932405</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>251.78005605239298</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>869845.3180691048</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>692846.7069175455</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.7965171422150512</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.7965171422150511</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>4815.226020083</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.331352510226805</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2144.6306589285373</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>4815.226020083</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2169.7818596842108</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$349,A8,'Species'!$U$2:$U$349))</x:f>
-        <x:v>10447990.068655493</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.331352510226805</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2144.6306589285373</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>10326881.352340441</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>121108.71631505154</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0117275208441903</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.011727520844190193</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1950.5847957591998</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.826043817712371</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>669.9522001715823</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1950.5847957591998</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>699.438651080431</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$349,A9,'Species'!$U$2:$U$349))</x:f>
-        <x:v>1364314.3983638126</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.826043817712371</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>669.9522001715823</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1306798.5755401123</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>57515.82282370026</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0440127682262956</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.04401276822629564</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>72.98124156180002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8876894387453627</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>772.1282435768085</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>72.98124156180002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>792.9155021934758</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$349,A10,'Species'!$U$2:$U$349))</x:f>
-        <x:v>57867.95780367803</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8876894387453627</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>772.1282435768085</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>56350.87786116742</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1517.0799425106088</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0269220285484861</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.02692202854848621</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>8162.371886412899</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.07781599929058</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1196.2336069151352</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>8162.371886412899</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1323.220703232419</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$349,A11,'Species'!$U$2:$U$349))</x:f>
-        <x:v>10800619.467583803</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.07781599929058</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1196.2336069151352</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>9764103.562666398</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1036515.9049174059</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.106155767220719</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.10615576722071887</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>6567.941259942998</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.0411330002352934</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>109.9342455312248</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>6567.941259942998</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>135.1509274008054</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$349,A12,'Species'!$U$2:$U$349))</x:f>
-        <x:v>887663.3523953104</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.0411330002352934</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>109.9342455312248</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>722041.6671052355</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>165621.6852900749</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.2293796782588393</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.22937967825883934</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>8612.7640875372</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.446679443897913</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2796.916132223337</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>8612.7640875372</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2847.344192208329</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$349,A13,'Species'!$U$2:$U$349))</x:f>
-        <x:v>24523503.803509515</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.446679443897913</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2796.916132223337</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>24089178.819466606</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>434324.984042909</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.018029879195879</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.018029879195878958</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>360.6890141525</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.075384026103708</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1189.5536286214121</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>360.6890141525</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1193.3335197545953</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$349,A14,'Species'!$U$2:$U$349))</x:f>
-        <x:v>430422.2907954179</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.075384026103708</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1189.5536286214121</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>429058.92558898625</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1363.3652064316557</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0031775710167552</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.003177571016755123</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>15867.9949951432</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.937669481298999</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>866.3023276529287</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>15867.9949951432</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1247.1416191222672</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$349,A15,'Species'!$U$2:$U$349))</x:f>
-        <x:v>19789636.970466923</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.937669481298999</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>866.3023276529287</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>13746480.999477578</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>6043155.970989345</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.439614761859345</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.4396147618593449</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>36867.411067038694</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.5286788453329168</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>337.8149344205835</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>36867.411067038694</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>428.12646900073645</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$349,A16,'Species'!$U$2:$U$349))</x:f>
-        <x:v>15783914.52132995</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.5286788453329168</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>337.8149344205835</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>12454362.05186837</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>3329552.4694615807</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2673402664540405</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.2673402664540405</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>50815.7592961461</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.6131386345947045</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>410.3350684020551</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>50815.7592961461</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>531.1454337593838</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$349,A17,'Species'!$U$2:$U$349))</x:f>
-        <x:v>26990558.513163954</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.6131386345947045</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>410.3350684020551</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>20851488.066686474</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>6139070.44647748</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.2944188168654307</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.29441881686543075</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>4009.8326831342</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.0037438597257013</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>100.86578195858428</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>4009.8326831342</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>152.59907722543258</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$349,A18,'Species'!$U$2:$U$349))</x:f>
-        <x:v>611896.7672746594</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.0037438597257013</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>100.86578195858428</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>404454.9091074192</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>207441.85816724016</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.5128924226066092</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.5128924226066092</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>32017.7068465829</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.4230518857819856</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>26.488165776030176</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>32017.7068465829</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>134.77257225268352</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$349,A19,'Species'!$U$2:$U$349))</x:f>
-        <x:v>4315108.7093463335</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.4230518857819856</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>26.488165776030176</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>848090.3267206242</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>3467018.3826257093</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>5.088029627730686</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>4.088029627730686</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>4301.503147629</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.8414826822871713</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>69.4196919707794</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>4301.503147629</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>80.49125119795269</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$349,A20,'Species'!$U$2:$U$349))</x:f>
-        <x:v>346233.37038459</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.8414826822871713</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>69.4196919707794</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>298609.0235197432</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>47624.346864846826</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.1594872998260148</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.15948729982601495</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.2384825837</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.54</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>346.73685045253166</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.2384825837</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$349,A21,'Species'!$U$2:$U$349))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>82.69069995992027</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.54</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>82.69069995992027</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>2.2788573946999997</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.3845426128129286</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>242.40558003392073</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>2.2788573946999997</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>243.23320559890155</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$349,A22,'Species'!$U$2:$U$349))</x:f>
-        <x:v>554.2937892156422</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.3845426128129286</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>242.40558003392073</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>552.4077485768429</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1.8860406387992725</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0034142182901276</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.003414218290127612</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>10.8522665506</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.305475402367786</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>202.05769870264982</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>10.8522665506</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>259.3208055754212</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$349,A23,'Species'!$U$2:$U$349))</x:f>
-        <x:v>2814.2185042207893</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.305475402367786</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>202.05769870264982</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>2192.7840049219794</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>621.4344992988099</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.2833997775904613</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.28339977759046125</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>29105.506389645296</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.0740072637850777</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>118.5788580888338</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>29105.506389645296</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>118.87766234036742</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$349,A24,'Species'!$U$2:$U$349))</x:f>
-        <x:v>3459994.56083366</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.0740072637850777</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>118.5788580888338</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>3451297.7117813947</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>8696.849052265286</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0025198779643314</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.0025198779643313906</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>1.1986246704</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.2777511244357243</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>189.56193116688314</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>1.1986246704</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>239.2719819657858</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$349,A25,'Species'!$U$2:$U$349))</x:f>
-        <x:v>286.7973005196948</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.2777511244357243</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>189.56193116688314</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>227.2136072652928</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>59.583693254401965</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.262236465375212</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.26223646537521195</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>14425.125433030898</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.4296593175747145</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>268.9424256630676</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>14425.125433030898</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>380.88046800376395</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$349,A26,'Species'!$U$2:$U$349))</x:f>
-        <x:v>5494248.525945807</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.4296593175747145</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>268.9424256630676</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>3879528.224453338</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>1614720.301492469</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.416215634497671</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.41621563449767096</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
       <x:c r="A27" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B27" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="n">
+      <x:c r="B27" s="31" t="n">
         <x:v>1950.0104460378998</x:v>
       </x:c>
+      <x:c r="C27" s="32" t="n">
+        <x:v>4.081993004716131</x:v>
+      </x:c>
+      <x:c r="D27" s="32" t="n">
+        <x:f>IF(C27="","",(1/'Metadata'!$B$5)^(C27-1))</x:f>
+        <x:v>1207.7943807205409</x:v>
+      </x:c>
       <x:c r="E27" s="31" t="n">
-        <x:v>1950.0104460378998</x:v>
-      </x:c>
-      <x:c r="F27" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="32" t="n">
-        <x:f>IF(E27=0,"",I27/E27)</x:f>
-        <x:v>1315.2610303043027</x:v>
-      </x:c>
-      <x:c r="I27" s="31" t="n">
-        <x:f>IF(C27=0,"",SUMIF('Species'!$G$2:$G$349,A27,'Species'!$U$2:$U$349))</x:f>
-        <x:v>2564772.748359961</x:v>
-      </x:c>
-      <x:c r="J27" s="32" t="n">
-        <x:v>4.081993004716131</x:v>
-      </x:c>
-      <x:c r="K27" s="32" t="n">
-        <x:f>IF(J27="","",(1/'Metadata'!$B$5)^(J27-1))</x:f>
-        <x:v>1207.7943807205409</x:v>
-      </x:c>
-      <x:c r="L27" s="31" t="n">
-        <x:f>IF(E27=0,"",E27*K27)</x:f>
+        <x:f>IF(B27=0,"",B27*D27)</x:f>
         <x:v>2355211.659070931</x:v>
-      </x:c>
-      <x:c r="M27" s="31" t="n">
-        <x:f>IF(E27=0,"",I27-L27)</x:f>
-        <x:v>209561.08928903006</x:v>
-      </x:c>
-      <x:c r="N27" s="32" t="n">
-        <x:f>IF(L27=0,"",I27/L27)</x:f>
-        <x:v>1.0889776035550438</x:v>
-      </x:c>
-      <x:c r="O27" s="34" t="n">
-        <x:f>IF(L27=0,"",M27/L27)</x:f>
-        <x:v>0.08897760355504371</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="18" customHeight="1">
       <x:c r="A28" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B28" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C28" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D28" s="31" t="n">
+      <x:c r="B28" s="31" t="n">
         <x:v>2394.7167847299997</x:v>
       </x:c>
+      <x:c r="C28" s="32" t="n">
+        <x:v>3.823761347003524</x:v>
+      </x:c>
+      <x:c r="D28" s="32" t="n">
+        <x:f>IF(C28="","",(1/'Metadata'!$B$5)^(C28-1))</x:f>
+        <x:v>666.4404469962747</x:v>
+      </x:c>
       <x:c r="E28" s="31" t="n">
-        <x:v>2394.7167847299997</x:v>
-      </x:c>
-      <x:c r="F28" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G28" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H28" s="32" t="n">
-        <x:f>IF(E28=0,"",I28/E28)</x:f>
-        <x:v>667.1401966023049</x:v>
-      </x:c>
-      <x:c r="I28" s="31" t="n">
-        <x:f>IF(C28=0,"",SUMIF('Species'!$G$2:$G$349,A28,'Species'!$U$2:$U$349))</x:f>
-        <x:v>1597611.8265716115</x:v>
-      </x:c>
-      <x:c r="J28" s="32" t="n">
-        <x:v>3.823761347003524</x:v>
-      </x:c>
-      <x:c r="K28" s="32" t="n">
-        <x:f>IF(J28="","",(1/'Metadata'!$B$5)^(J28-1))</x:f>
-        <x:v>666.4404469962747</x:v>
-      </x:c>
-      <x:c r="L28" s="31" t="n">
-        <x:f>IF(E28=0,"",E28*K28)</x:f>
+        <x:f>IF(B28=0,"",B28*D28)</x:f>
         <x:v>1595936.1244449427</x:v>
       </x:c>
-      <x:c r="M28" s="31" t="n">
-        <x:f>IF(E28=0,"",I28-L28)</x:f>
-        <x:v>1675.7021266687661</x:v>
-      </x:c>
-      <x:c r="N28" s="32" t="n">
-        <x:f>IF(L28=0,"",I28/L28)</x:f>
-        <x:v>1.0010499806984767</x:v>
-      </x:c>
-      <x:c r="O28" s="34" t="n">
-        <x:f>IF(L28=0,"",M28/L28)</x:f>
-        <x:v>0.001049980698476617</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G28">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O28">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99cf0eaa27604da7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf56717ba7f346eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26471,7 +24952,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -26570,7 +25051,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>220204619.0813138</x:v>
+        <x:v>169005621.09511688</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26584,7 +25065,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>220204619.0813137</x:v>
+        <x:v>189192339.3498306</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26598,7 +25079,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>8.940696716308594e-8</x:v>
+        <x:v>-51198997.986196816</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26612,7 +25093,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-31012279.7314831</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26623,9 +25104,9 @@
         <x:v>EEZ_919</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -26637,47 +25118,19 @@
         <x:v>EEZ_919</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_919</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_919</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a1ea376713d4b96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd1c8ff19fae4e9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26724,7 +25177,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
